--- a/artfynd/A 1221-2026 artfynd.xlsx
+++ b/artfynd/A 1221-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136439755</v>
       </c>
       <c r="B4" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1221-2026 artfynd.xlsx
+++ b/artfynd/A 1221-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136439755</v>
       </c>
       <c r="B4" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1221-2026 artfynd.xlsx
+++ b/artfynd/A 1221-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136439755</v>
       </c>
       <c r="B4" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1221-2026 artfynd.xlsx
+++ b/artfynd/A 1221-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136439755</v>
       </c>
       <c r="B4" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1221-2026 artfynd.xlsx
+++ b/artfynd/A 1221-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136439755</v>
       </c>
       <c r="B4" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1221-2026 artfynd.xlsx
+++ b/artfynd/A 1221-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136439755</v>
       </c>
       <c r="B4" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1221-2026 artfynd.xlsx
+++ b/artfynd/A 1221-2026 artfynd.xlsx
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elvira Ljungberg, Jennifer Gao</t>
+          <t>Jennifer Gao, Elvira Ljungberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 1221-2026 artfynd.xlsx
+++ b/artfynd/A 1221-2026 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>136439755</v>
       </c>
       <c r="B4" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jennifer Gao, Elvira Ljungberg</t>
+          <t>Elvira Ljungberg, Jennifer Gao</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
